--- a/Categoría/UOcc_Categoría.xlsx
+++ b/Categoría/UOcc_Categoría.xlsx
@@ -833,13 +833,13 @@
         <v>0.3412141440273959</v>
       </c>
       <c r="C2" s="2">
-        <v>112.2262160580291</v>
+        <v>112.3873458359547</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.38293172249674</v>
+        <v>0.3834815200892618</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1003,13 +1003,13 @@
         <v>3.965656987908054</v>
       </c>
       <c r="C12" s="2">
-        <v>114.0260936974023</v>
+        <v>114.0260936974022</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="2">
-        <v>4.521883752749618</v>
+        <v>4.521883752749617</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1071,7 +1071,7 @@
         <v>1.402305332271666</v>
       </c>
       <c r="C16" s="2">
-        <v>110.1299823601237</v>
+        <v>110.1299823601238</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>6</v>
@@ -2173,7 +2173,7 @@
         <v>85</v>
       </c>
       <c r="B81" s="2">
-        <v>0.2796309029096915</v>
+        <v>0.2796309029096916</v>
       </c>
       <c r="C81" s="2">
         <v>106.7551857842833</v>
@@ -2292,7 +2292,7 @@
         <v>92</v>
       </c>
       <c r="B88" s="2">
-        <v>0.9710206158672994</v>
+        <v>0.9710206158672995</v>
       </c>
       <c r="C88" s="2">
         <v>106.0139722125379</v>
@@ -2836,7 +2836,7 @@
         <v>124</v>
       </c>
       <c r="B120" s="2">
-        <v>2.042392758113714</v>
+        <v>2.042392758113713</v>
       </c>
       <c r="C120" s="2">
         <v>113.0788339564436</v>
@@ -2845,7 +2845,7 @@
         <v>6</v>
       </c>
       <c r="E120" s="2">
-        <v>2.309513915685835</v>
+        <v>2.309513915685836</v>
       </c>
     </row>
     <row r="121" spans="1:5">
